--- a/34_GLOBAL_EX/CHEX_Productivity/CHEX Material Density v1.0 14102026.xlsx
+++ b/34_GLOBAL_EX/CHEX_Productivity/CHEX Material Density v1.0 14102026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnhind-my.sharepoint.com/personal/tavinder_arora_cnhind_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnhind-my.sharepoint.com/personal/tavinder_arora_cnhind_com/Documents/Desktop/attachmentscnh/34_GLOBAL_EX/CHEX_Productivity/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{FA7420F5-155E-4E62-89CE-AAFD529687AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A203F609-5169-42BB-9A10-15497BE61FE2}"/>
